--- a/data/trans_dic/P19D_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>90,76; 95,34</t>
+          <t>90,48; 95,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81,57; 87,66</t>
+          <t>81,46; 87,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86,38; 91,87</t>
+          <t>86,4; 91,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,47; 93,11</t>
+          <t>87,67; 92,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,12; 96,21</t>
+          <t>92,13; 96,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,81; 90,51</t>
+          <t>84,94; 90,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,6; 93,75</t>
+          <t>88,71; 93,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,34; 95,92</t>
+          <t>93,05; 95,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,96; 95,28</t>
+          <t>92,19; 95,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84,22; 88,24</t>
+          <t>84,02; 88,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88,28; 91,99</t>
+          <t>88,35; 92,06</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,95; 94,05</t>
+          <t>91,1; 93,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>91,08; 95,02</t>
+          <t>91,49; 94,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82,58; 87,54</t>
+          <t>82,79; 87,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89,29; 93,4</t>
+          <t>89,28; 93,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,7; 92,82</t>
+          <t>89,52; 93,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,13; 94,99</t>
+          <t>91,2; 94,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,76; 90,04</t>
+          <t>85,44; 90,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,3; 93,08</t>
+          <t>89,14; 93,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,82; 95,57</t>
+          <t>92,64; 95,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>91,97; 94,51</t>
+          <t>91,85; 94,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84,95; 88,27</t>
+          <t>85,06; 88,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>89,87; 92,73</t>
+          <t>89,99; 92,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>56,81; 93,45</t>
+          <t>91,7; 93,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,91; 93,42</t>
+          <t>88,44; 93,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,88; 87,83</t>
+          <t>82,01; 87,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88,51; 93,62</t>
+          <t>88,19; 93,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89,26; 94,51</t>
+          <t>89,1; 94,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>91,08; 95,23</t>
+          <t>91,17; 95,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,09; 92,02</t>
+          <t>87,38; 92,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,17; 94,73</t>
+          <t>90,33; 94,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94,46; 98,3</t>
+          <t>93,41; 96,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,51; 93,84</t>
+          <t>90,55; 93,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,6; 89,43</t>
+          <t>85,66; 89,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>90,23; 93,58</t>
+          <t>90,15; 93,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>92,85; 96,53</t>
+          <t>92,0; 94,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>90,86; 94,58</t>
+          <t>90,88; 94,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>86,99; 91,56</t>
+          <t>87,39; 91,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,64; 92,21</t>
+          <t>87,88; 92,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89,13; 93,71</t>
+          <t>89,48; 93,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,56; 93,53</t>
+          <t>89,73; 93,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,11; 92,07</t>
+          <t>87,94; 92,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,61; 91,79</t>
+          <t>87,45; 91,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,46; 95,04</t>
+          <t>92,04; 94,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,67; 93,5</t>
+          <t>90,89; 93,5</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88,26; 91,2</t>
+          <t>88,41; 91,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88,27; 91,3</t>
+          <t>88,22; 91,33</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,13; 94,02</t>
+          <t>91,23; 93,52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>91,65; 93,72</t>
+          <t>91,57; 93,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,06; 87,7</t>
+          <t>84,89; 87,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89,4; 91,77</t>
+          <t>89,51; 91,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63,3; 92,13</t>
+          <t>90,32; 92,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>92,04; 93,99</t>
+          <t>91,98; 93,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,88; 90,11</t>
+          <t>87,81; 90,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,05; 92,15</t>
+          <t>90,06; 92,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,78; 95,73</t>
+          <t>93,44; 94,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>92,14; 93,52</t>
+          <t>92,12; 93,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86,92; 88,65</t>
+          <t>86,78; 88,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90,17; 91,64</t>
+          <t>90,02; 91,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>78,5; 93,64</t>
+          <t>92,17; 93,49</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>557750</t>
+          <t>600100</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>616995</t>
+          <t>667089</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1174745</t>
+          <t>1267189</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>433671; 455555</t>
+          <t>432332; 455522</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>492737; 529552</t>
+          <t>492105; 529756</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>453466; 482301</t>
+          <t>453588; 482284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>537360; 572005</t>
+          <t>580826; 614174</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>495725; 517700</t>
+          <t>495731; 517957</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>538301; 574488</t>
+          <t>539167; 575545</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>482324; 510336</t>
+          <t>482878; 508810</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>607518; 624354</t>
+          <t>656463; 675873</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>934243; 967974</t>
+          <t>936578; 967650</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1043304; 1093138</t>
+          <t>1040898; 1092850</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>943989; 983704</t>
+          <t>944793; 984397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1150687; 1189961</t>
+          <t>1246312; 1284640</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>847418</t>
+          <t>930870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>892786</t>
+          <t>988607</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1740205</t>
+          <t>1919477</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>657692; 686168</t>
+          <t>660665; 685744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>714083; 756970</t>
+          <t>715911; 759586</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>728926; 762450</t>
+          <t>728810; 762805</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>463093; 1082897</t>
+          <t>909657; 948205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>732879; 763921</t>
+          <t>733443; 762742</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>772687; 811176</t>
+          <t>769795; 811485</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>773629; 806461</t>
+          <t>772321; 806297</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>878113; 904177</t>
+          <t>973765; 1000838</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1403810; 1442555</t>
+          <t>1401895; 1443040</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1499998; 1558627</t>
+          <t>1501909; 1559078</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1512195; 1560469</t>
+          <t>1514247; 1561549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1200104; 1974212</t>
+          <t>1895693; 1940535</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634029</t>
+          <t>711898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>890876</t>
+          <t>761623</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1524905</t>
+          <t>1473521</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>479214; 509228</t>
+          <t>482064; 509307</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>519964; 557733</t>
+          <t>520829; 558469</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>486177; 514286</t>
+          <t>484422; 514137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>612676; 648702</t>
+          <t>688957; 727913</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>532451; 556731</t>
+          <t>532966; 556524</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>591707; 625248</t>
+          <t>593691; 626672</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>521616; 547988</t>
+          <t>522545; 547959</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>874308; 909872</t>
+          <t>748096; 771691</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1022503; 1060054</t>
+          <t>1022957; 1057621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1125249; 1175584</t>
+          <t>1125956; 1177395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1017593; 1055349</t>
+          <t>1016693; 1053356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1496773; 1556014</t>
+          <t>1448174; 1493111</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>815652</t>
+          <t>863003</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>991578</t>
+          <t>999822</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1807230</t>
+          <t>1862824</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>646955; 673443</t>
+          <t>647127; 672512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>699139; 735804</t>
+          <t>702316; 737529</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>676368; 711561</t>
+          <t>678189; 710520</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>790580; 831209</t>
+          <t>843974; 880060</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>728985; 761301</t>
+          <t>730388; 760597</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>818029; 854759</t>
+          <t>816373; 854193</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>768232; 804884</t>
+          <t>766827; 803547</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>969884; 1007859</t>
+          <t>985677; 1012492</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1383618; 1426776</t>
+          <t>1387061; 1426831</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1528717; 1579649</t>
+          <t>1531341; 1582612</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1455182; 1505068</t>
+          <t>1454392; 1505669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1774657; 1831011</t>
+          <t>1837489; 1883676</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2854849</t>
+          <t>3105870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3392236</t>
+          <t>3417140</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6247085</t>
+          <t>6523010</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2251886; 2302857</t>
+          <t>2249837; 2300234</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2473137; 2549828</t>
+          <t>2468125; 2545943</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2380281; 2443382</t>
+          <t>2383071; 2443180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2123195; 3090183</t>
+          <t>3066293; 3138379</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2522663; 2576218</t>
+          <t>2521152; 2574645</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2762378; 2832521</t>
+          <t>2760393; 2831392</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2580896; 2641074</t>
+          <t>2581069; 2641585</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3360304; 3429908</t>
+          <t>3390242; 3440254</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4789258; 4861204</t>
+          <t>4788556; 4865565</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5259369; 5364415</t>
+          <t>5250889; 5360122</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4985241; 5066508</t>
+          <t>4976550; 5064315</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5446122; 6496025</t>
+          <t>6473295; 6566293</t>
         </is>
       </c>
     </row>
